--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I16" s="14">
+        <v>15</v>
+      </c>
+      <c r="J16" s="14">
         <v>11</v>
       </c>
-      <c r="J16" s="14">
-        <v>10</v>
-      </c>
       <c r="K16" s="15">
-        <v>10</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L16" s="15">
-        <v>57.142857142857</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.428571428571</v>
+        <v>-6.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.539682539682</v>
+        <v>-79.452054794520</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="I17" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" s="15">
-        <v>87.5</v>
+        <v>122.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>15.384615384615</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N17" s="15">
-        <v>87.5</v>
+        <v>122.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="F18" s="14">
+        <v>15</v>
+      </c>
+      <c r="G18" s="14">
+        <v>20</v>
+      </c>
+      <c r="H18" s="15">
         <v>-25</v>
       </c>
-      <c r="F18" s="14">
-        <v>12</v>
-      </c>
-      <c r="G18" s="14">
-        <v>17</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-29.411764705882</v>
-      </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="M18" s="15">
-        <v>29.411764705882</v>
+        <v>23.809523809523</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.595744680851</v>
+        <v>-76.363636363636</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
         <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>25</v>
+        <v>41.025641025641</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K19" s="15">
-        <v>26.229508196721</v>
+        <v>38.805970149253</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.465116279069</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M19" s="15">
-        <v>-18.085106382978</v>
+        <v>-9.708737864077</v>
       </c>
       <c r="N19" s="15">
-        <v>-66.521739130434</v>
+        <v>-65.555555555555</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.727272727272</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>15</v>
+        <v>107.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>11.842105263157</v>
+        <v>36.231884057971</v>
       </c>
       <c r="I21" s="17">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="J21" s="17">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="K21" s="18">
-        <v>23.076923076923</v>
+        <v>33.898305084745</v>
       </c>
       <c r="L21" s="18">
-        <v>4.065040650406</v>
+        <v>15.328467153284</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.571428571428</v>
+        <v>1.935483870967</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.849056603773</v>
+        <v>-74.72</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14">
         <v>4</v>
       </c>
       <c r="K23" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
         <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.090909090909</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>25.974025974026</v>
+        <v>-1.315789473684</v>
       </c>
       <c r="I24" s="14">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="J24" s="14">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="K24" s="15">
-        <v>21.487603305785</v>
+        <v>12.587412587412</v>
       </c>
       <c r="L24" s="15">
-        <v>20.491803278688</v>
+        <v>11.034482758620</v>
       </c>
       <c r="M24" s="15">
-        <v>32.432432432432</v>
+        <v>30.894308943089</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
         <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-27.777777777777</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="14">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.219178082191</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="I25" s="14">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>-6.4</v>
       </c>
       <c r="L25" s="15">
-        <v>13.829787234042</v>
+        <v>3.539823008849</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>57.142857142857</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J26" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K26" s="15">
-        <v>13.636363636363</v>
+        <v>7.407407407407</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="M26" s="15">
-        <v>19.047619047619</v>
+        <v>7.407407407407</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1409,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
         <v>-100</v>
@@ -1437,14 +1437,14 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="14">
-        <v>2</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1570,7 +1570,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1579,7 +1579,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,73 +904,73 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14">
+        <v>1</v>
       </c>
       <c r="J15" s="14">
         <v>1</v>
       </c>
       <c r="K15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>4</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>233.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="L16" s="15">
-        <v>114.285714285714</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M16" s="15">
         <v>-6.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.452054794520</v>
+        <v>-82.758620689655</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
         <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" s="15">
-        <v>122.222222222222</v>
+        <v>110</v>
       </c>
       <c r="L17" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M17" s="15">
-        <v>53.846153846153</v>
+        <v>50</v>
       </c>
       <c r="N17" s="15">
-        <v>122.222222222222</v>
+        <v>90.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>6</v>
-      </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>62.5</v>
+        <v>21.739130434782</v>
       </c>
       <c r="M18" s="15">
-        <v>23.809523809523</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.363636363636</v>
+        <v>-77.952755905511</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>41.025641025641</v>
+        <v>11.320754716981</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="J19" s="14">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>38.805970149253</v>
+        <v>27.058823529411</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.060606060606</v>
+        <v>-0.917431192660</v>
       </c>
       <c r="M19" s="15">
-        <v>-9.708737864077</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.555555555555</v>
+        <v>-65.048543689320</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
-        <v>2</v>
-      </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M20" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.5</v>
+        <v>-96.703296703296</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>107.142857142857</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>36.231884057971</v>
+        <v>17.721518987341</v>
       </c>
       <c r="I21" s="17">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="J21" s="17">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="K21" s="18">
-        <v>33.898305084745</v>
+        <v>26.056338028169</v>
       </c>
       <c r="L21" s="18">
-        <v>15.328467153284</v>
+        <v>8.484848484848</v>
       </c>
       <c r="M21" s="18">
-        <v>1.935483870967</v>
+        <v>5.917159763313</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.72</v>
+        <v>-75.138888888888</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,17 +1185,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1204,7 +1204,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
         <v>-100</v>
@@ -1223,8 +1223,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1251,7 +1251,7 @@
         <v>-25</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="M23" s="15">
         <v>-40</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.315789473684</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="I24" s="14">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J24" s="14">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="K24" s="15">
-        <v>12.587412587412</v>
+        <v>4.142011834319</v>
       </c>
       <c r="L24" s="15">
-        <v>11.034482758620</v>
+        <v>1.149425287356</v>
       </c>
       <c r="M24" s="15">
-        <v>30.894308943089</v>
+        <v>32.330827067669</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.058823529411</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="I25" s="14">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="J25" s="14">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="L25" s="15">
-        <v>3.539823008849</v>
+        <v>-0.751879699248</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>-20</v>
+        <v>300</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="I26" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J26" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K26" s="15">
-        <v>7.407407407407</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.451612903225</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M26" s="15">
-        <v>7.407407407407</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I27" s="14">
+        <v>1</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+        <v>-66.666666666666</v>
+      </c>
+      <c r="L27" s="15">
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
+      </c>
+      <c r="F28" s="14">
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>25</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>7.142857142857</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.758620689655</v>
+        <v>-82.105263157894</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
         <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="15">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I17" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K17" s="15">
-        <v>110</v>
+        <v>127.272727272727</v>
       </c>
       <c r="L17" s="15">
-        <v>50</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>90.909090909090</v>
+        <v>78.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,31 +1028,31 @@
         <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
         <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-27.777777777777</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>-6.666666666666</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="L18" s="15">
-        <v>21.739130434782</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M18" s="15">
-        <v>3.703703703703</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.952755905511</v>
+        <v>-80.405405405405</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,72 +1060,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>11.320754716981</v>
+        <v>19.230769230769</v>
       </c>
       <c r="I19" s="14">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>27.058823529411</v>
+        <v>19.801980198019</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.917431192660</v>
+        <v>0</v>
       </c>
       <c r="M19" s="15">
-        <v>-1.818181818181</v>
+        <v>-2.419354838709</v>
       </c>
       <c r="N19" s="15">
-        <v>-65.048543689320</v>
+        <v>-64.723032069970</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
         <v>50</v>
@@ -1134,7 +1134,7 @@
         <v>500</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.703296703296</v>
+        <v>-97.044334975369</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1151,31 +1151,31 @@
         <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>17.721518987341</v>
+        <v>14.634146341463</v>
       </c>
       <c r="I21" s="17">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="J21" s="17">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="K21" s="18">
-        <v>26.056338028169</v>
+        <v>19.879518072289</v>
       </c>
       <c r="L21" s="18">
-        <v>8.484848484848</v>
+        <v>3.108808290155</v>
       </c>
       <c r="M21" s="18">
-        <v>5.917159763313</v>
+        <v>5.851063829787</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.138888888888</v>
+        <v>-75.340768277571</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,17 +1185,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="14">
-        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.072289156626</v>
+        <v>-20.212765957446</v>
       </c>
       <c r="I24" s="14">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="J24" s="14">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="K24" s="15">
-        <v>4.142011834319</v>
+        <v>4.663212435233</v>
       </c>
       <c r="L24" s="15">
-        <v>1.149425287356</v>
+        <v>1</v>
       </c>
       <c r="M24" s="15">
-        <v>32.330827067669</v>
+        <v>35.570469798657</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>56.25</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G25" s="14">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>-24.324324324324</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="J25" s="14">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="K25" s="15">
-        <v>-12</v>
+        <v>-5.421686746987</v>
       </c>
       <c r="L25" s="15">
-        <v>-0.751879699248</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>300</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H26" s="15">
         <v>20</v>
       </c>
       <c r="I26" s="14">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J26" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K26" s="15">
-        <v>14.285714285714</v>
+        <v>13.888888888888</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.030303030303</v>
+        <v>17.142857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>6.666666666666</v>
+        <v>13.888888888888</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>200</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>5</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>200</v>
       </c>
       <c r="L31" s="15">
         <v>200</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -898,29 +898,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,10 +937,10 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
@@ -949,69 +949,69 @@
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>21.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L16" s="15">
-        <v>13.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M16" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.105263157894</v>
+        <v>-83.636363636363</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>4</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
         <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I17" s="14">
         <v>25</v>
       </c>
       <c r="J17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K17" s="15">
-        <v>127.272727272727</v>
+        <v>108.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>38.888888888888</v>
+        <v>25</v>
       </c>
       <c r="M17" s="15">
-        <v>78.571428571428</v>
+        <v>56.25</v>
       </c>
       <c r="N17" s="15">
-        <v>78.571428571428</v>
+        <v>47.058823529411</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-44.444444444444</v>
+        <v>-43.75</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.705882352941</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.121212121212</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M18" s="15">
-        <v>-6.451612903225</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.405405405405</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,78 +1063,78 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.75</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>19.230769230769</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I19" s="14">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="K19" s="15">
-        <v>19.801980198019</v>
+        <v>19.642857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>0</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="M19" s="15">
-        <v>-2.419354838709</v>
+        <v>-3.597122302158</v>
       </c>
       <c r="N19" s="15">
-        <v>-64.723032069970</v>
+        <v>-64.736842105263</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>500</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.044334975369</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>14.634146341463</v>
+        <v>10.126582278481</v>
       </c>
       <c r="I21" s="17">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="K21" s="18">
-        <v>19.879518072289</v>
+        <v>18.579234972677</v>
       </c>
       <c r="L21" s="18">
-        <v>3.108808290155</v>
+        <v>1.877934272300</v>
       </c>
       <c r="M21" s="18">
-        <v>5.851063829787</v>
+        <v>2.843601895734</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.340768277571</v>
+        <v>-75.808249721293</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
+        <v>-75</v>
+      </c>
+      <c r="I22" s="14">
+        <v>1</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L22" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="M23" s="15">
         <v>-33.333333333333</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-20</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.212765957446</v>
+        <v>-25.471698113207</v>
       </c>
       <c r="I24" s="14">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="J24" s="14">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="K24" s="15">
-        <v>4.663212435233</v>
+        <v>-1.321585903083</v>
       </c>
       <c r="L24" s="15">
-        <v>1</v>
+        <v>4.672897196261</v>
       </c>
       <c r="M24" s="15">
-        <v>35.570469798657</v>
+        <v>30.994152046783</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>56.25</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="F25" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.181818181818</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J25" s="14">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.421686746987</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>3.012048192771</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>20</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K26" s="15">
-        <v>13.888888888888</v>
+        <v>32.5</v>
       </c>
       <c r="L26" s="15">
-        <v>17.142857142857</v>
+        <v>35.897435897435</v>
       </c>
       <c r="M26" s="15">
-        <v>13.888888888888</v>
+        <v>29.268292682926</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,32 +1390,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
+        <v>-80</v>
+      </c>
+      <c r="L27" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
+        <v>100</v>
+      </c>
+      <c r="I28" s="14">
+        <v>6</v>
+      </c>
+      <c r="J28" s="14">
+        <v>5</v>
+      </c>
+      <c r="K28" s="15">
+        <v>20</v>
+      </c>
+      <c r="L28" s="15">
         <v>200</v>
-      </c>
-      <c r="I28" s="14">
-        <v>5</v>
-      </c>
-      <c r="J28" s="14">
-        <v>4</v>
-      </c>
-      <c r="K28" s="15">
-        <v>25</v>
-      </c>
-      <c r="L28" s="15">
-        <v>150</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,35 +1551,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="C31" s="14">
+        <v>3</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1637,8 +1637,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,123 +895,123 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L15" s="15">
+        <v>0</v>
+      </c>
+      <c r="M15" s="15">
+        <v>100</v>
+      </c>
+      <c r="N15" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="14">
         <v>7</v>
       </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
+        <v>17</v>
+      </c>
+      <c r="J16" s="14">
         <v>18</v>
       </c>
-      <c r="J16" s="14">
-        <v>15</v>
-      </c>
       <c r="K16" s="15">
-        <v>20</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>20</v>
+        <v>6.25</v>
       </c>
       <c r="M16" s="15">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.636363636363</v>
+        <v>-85.470085470085</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="15">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K17" s="15">
-        <v>108.333333333333</v>
+        <v>92.857142857142</v>
       </c>
       <c r="L17" s="15">
-        <v>25</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M17" s="15">
-        <v>56.25</v>
+        <v>68.75</v>
       </c>
       <c r="N17" s="15">
-        <v>47.058823529411</v>
+        <v>42.105263157894</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,31 +1028,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-43.75</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.882352941176</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-80</v>
+        <v>-80.898876404494</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>18.181818181818</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F19" s="14">
         <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>11.764705882352</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K19" s="15">
-        <v>19.642857142857</v>
+        <v>23.966942148760</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.470588235294</v>
+        <v>-0.662251655629</v>
       </c>
       <c r="M19" s="15">
-        <v>-3.597122302158</v>
+        <v>0</v>
       </c>
       <c r="N19" s="15">
-        <v>-64.736842105263</v>
+        <v>-63.855421686747</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1110,31 +1110,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
         <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L20" s="15">
-        <v>16.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.875</v>
+        <v>-96.385542168674</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,54 +1142,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="F21" s="17">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>10.126582278481</v>
+        <v>-2.469135802469</v>
       </c>
       <c r="I21" s="17">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="J21" s="17">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="K21" s="18">
-        <v>18.579234972677</v>
+        <v>20.100502512562</v>
       </c>
       <c r="L21" s="18">
-        <v>1.877934272300</v>
+        <v>1.702127659574</v>
       </c>
       <c r="M21" s="18">
-        <v>2.843601895734</v>
+        <v>7.657657657657</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.808249721293</v>
+        <v>-75.711382113821</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>-80</v>
       </c>
       <c r="L22" s="15">
-        <v>-83.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="M22" s="15">
         <v>-83.333333333333</v>
@@ -1226,20 +1226,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1251,7 +1251,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
         <v>-33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-32.352941176470</v>
+        <v>-16</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.471698113207</v>
+        <v>-20.183486238532</v>
       </c>
       <c r="I24" s="14">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="J24" s="14">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.321585903083</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="L24" s="15">
-        <v>4.672897196261</v>
+        <v>5.150214592274</v>
       </c>
       <c r="M24" s="15">
-        <v>30.994152046783</v>
+        <v>32.432432432432</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-51.724137931034</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F25" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G25" s="14">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-22.471910112359</v>
       </c>
       <c r="I25" s="14">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="J25" s="14">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.307692307692</v>
+        <v>-13.084112149532</v>
       </c>
       <c r="L25" s="15">
-        <v>3.012048192771</v>
+        <v>2.762430939226</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H26" s="15">
-        <v>55.555555555555</v>
+        <v>93.75</v>
       </c>
       <c r="I26" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J26" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K26" s="15">
-        <v>32.5</v>
+        <v>37.209302325581</v>
       </c>
       <c r="L26" s="15">
-        <v>35.897435897435</v>
+        <v>37.209302325581</v>
       </c>
       <c r="M26" s="15">
-        <v>29.268292682926</v>
+        <v>25.531914893617</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1432,31 +1432,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
-      <c r="H28" s="15">
-        <v>100</v>
-      </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1552,7 +1552,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1561,25 +1561,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,23 +895,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
@@ -939,20 +939,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
         <v>17</v>
@@ -964,13 +964,13 @@
         <v>-5.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>6.25</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M16" s="15">
         <v>-15</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.470085470085</v>
+        <v>-87.022900763358</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,31 +987,31 @@
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K17" s="15">
-        <v>92.857142857142</v>
+        <v>81.25</v>
       </c>
       <c r="L17" s="15">
-        <v>22.727272727272</v>
+        <v>16</v>
       </c>
       <c r="M17" s="15">
-        <v>68.75</v>
+        <v>81.25</v>
       </c>
       <c r="N17" s="15">
-        <v>42.105263157894</v>
+        <v>52.631578947368</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
+        <v>300</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>9</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>6</v>
-      </c>
-      <c r="G18" s="14">
-        <v>12</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-50</v>
-      </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.526315789473</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.108108108108</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="M18" s="15">
-        <v>6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.898876404494</v>
+        <v>-79.787234042553</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,78 +1063,78 @@
         <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>77.777777777777</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
         <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>5.555555555555</v>
+        <v>9.259259259259</v>
       </c>
       <c r="I19" s="14">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>23.966942148760</v>
+        <v>20.143884892086</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.662251655629</v>
+        <v>2.453987730061</v>
       </c>
       <c r="M19" s="15">
-        <v>0</v>
+        <v>3.726708074534</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.855421686747</v>
+        <v>-63.296703296703</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
-        <v>5</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
       <c r="H20" s="15">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
         <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.385542168674</v>
+        <v>-96.654275092936</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>43.75</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
+        <v>82</v>
+      </c>
+      <c r="G21" s="17">
         <v>79</v>
       </c>
-      <c r="G21" s="17">
-        <v>81</v>
-      </c>
       <c r="H21" s="18">
-        <v>-2.469135802469</v>
+        <v>3.797468354430</v>
       </c>
       <c r="I21" s="17">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="J21" s="17">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="K21" s="18">
-        <v>20.100502512562</v>
+        <v>18.552036199095</v>
       </c>
       <c r="L21" s="18">
-        <v>1.702127659574</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>7.657657657657</v>
+        <v>11.016949152542</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.711382113821</v>
+        <v>-75.468164794007</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,10 +1195,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>-80</v>
       </c>
       <c r="L22" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="M22" s="15">
         <v>-83.333333333333</v>
@@ -1251,7 +1251,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="15">
         <v>-33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-16</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.183486238532</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="I24" s="14">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="J24" s="14">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.777777777777</v>
+        <v>1.111111111111</v>
       </c>
       <c r="L24" s="15">
-        <v>5.150214592274</v>
+        <v>7.905138339920</v>
       </c>
       <c r="M24" s="15">
-        <v>32.432432432432</v>
+        <v>37.185929648241</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.052631578947</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="14">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.471910112359</v>
+        <v>-12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="J25" s="14">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.084112149532</v>
+        <v>-12.173913043478</v>
       </c>
       <c r="L25" s="15">
-        <v>2.762430939226</v>
+        <v>3.589743589743</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>93.75</v>
+        <v>70.588235294117</v>
       </c>
       <c r="I26" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K26" s="15">
-        <v>37.209302325581</v>
+        <v>35.555555555555</v>
       </c>
       <c r="L26" s="15">
-        <v>37.209302325581</v>
+        <v>22</v>
       </c>
       <c r="M26" s="15">
-        <v>25.531914893617</v>
+        <v>15.094339622641</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,23 +1387,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
@@ -1456,7 +1456,7 @@
         <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>4</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="L31" s="15">
         <v>500</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-66.666666666666</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>2</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.555555555555</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L16" s="15">
-        <v>-5.555555555555</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.022900763358</v>
+        <v>-87.586206896551</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
-      </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
-      <c r="E17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="14">
+        <v>5</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>8</v>
-      </c>
-      <c r="G17" s="14">
-        <v>6</v>
-      </c>
-      <c r="H17" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J17" s="14">
         <v>16</v>
       </c>
       <c r="K17" s="15">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="L17" s="15">
-        <v>16</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M17" s="15">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="N17" s="15">
-        <v>52.631578947368</v>
+        <v>36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-2.564102564102</v>
+        <v>2.439024390243</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.148936170212</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="15">
-        <v>11.764705882352</v>
+        <v>23.529411764705</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.787234042553</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
         <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>9.259259259259</v>
+        <v>22.916666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K19" s="15">
-        <v>20.143884892086</v>
+        <v>20.134228187919</v>
       </c>
       <c r="L19" s="15">
-        <v>2.453987730061</v>
+        <v>2.873563218390</v>
       </c>
       <c r="M19" s="15">
-        <v>3.726708074534</v>
+        <v>4.678362573099</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.296703296703</v>
+        <v>-63.617886178861</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>5</v>
+      </c>
+      <c r="G20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M20" s="15">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.654275092936</v>
+        <v>-96.232876712328</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>46.153846153846</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>3.797468354430</v>
+        <v>22.058823529411</v>
       </c>
       <c r="I21" s="17">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="J21" s="17">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="K21" s="18">
-        <v>18.552036199095</v>
+        <v>20.512820512820</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>1.438848920863</v>
       </c>
       <c r="M21" s="18">
-        <v>11.016949152542</v>
+        <v>14.17004048583</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.468164794007</v>
+        <v>-75.626620570440</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,10 +1210,10 @@
         <v>-80</v>
       </c>
       <c r="L22" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M22" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1232,14 +1232,14 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1251,7 +1251,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M23" s="15">
         <v>-33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>55.555555555555</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.980198019801</v>
+        <v>-8</v>
       </c>
       <c r="I24" s="14">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J24" s="14">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>1.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>7.905138339920</v>
+        <v>8.118081180811</v>
       </c>
       <c r="M24" s="15">
-        <v>37.185929648241</v>
+        <v>32.579185520362</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
         <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G25" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.5</v>
+        <v>-24.050632911392</v>
       </c>
       <c r="I25" s="14">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J25" s="14">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="K25" s="15">
-        <v>-12.173913043478</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>3.589743589743</v>
+        <v>0.462962962962</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="14">
         <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H26" s="15">
-        <v>70.588235294117</v>
+        <v>90.909090909090</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J26" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K26" s="15">
-        <v>35.555555555555</v>
+        <v>31.914893617021</v>
       </c>
       <c r="L26" s="15">
-        <v>22</v>
+        <v>21.568627450980</v>
       </c>
       <c r="M26" s="15">
-        <v>15.094339622641</v>
+        <v>14.814814814814</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
         <v>500</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -907,11 +907,11 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-50</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
@@ -929,48 +929,48 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="I16" s="14">
         <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.263157894736</v>
+        <v>-10</v>
       </c>
       <c r="L16" s="15">
+        <v>-28</v>
+      </c>
+      <c r="M16" s="15">
         <v>-14.285714285714</v>
       </c>
-      <c r="M16" s="15">
-        <v>-10</v>
-      </c>
       <c r="N16" s="15">
-        <v>-87.586206896551</v>
+        <v>-88.461538461538</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,31 +987,31 @@
         <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="I17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
         <v>16</v>
       </c>
       <c r="K17" s="15">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="L17" s="15">
-        <v>15.384615384615</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>87.5</v>
+        <v>68.421052631578</v>
       </c>
       <c r="N17" s="15">
-        <v>36.363636363636</v>
+        <v>23.076923076923</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>2.439024390243</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.5</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="M18" s="15">
-        <v>23.529411764705</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>-79</v>
+        <v>-79.245283018867</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,37 +1063,37 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>22.916666666666</v>
+        <v>1.785714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="J19" s="14">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="K19" s="15">
-        <v>20.134228187919</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>2.873563218390</v>
+        <v>3.783783783783</v>
       </c>
       <c r="M19" s="15">
-        <v>4.678362573099</v>
+        <v>3.225806451612</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.617886178861</v>
+        <v>-63.567362428842</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="15">
-        <v>83.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L20" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.232876712328</v>
+        <v>-96.091205211726</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>46.153846153846</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>22.058823529411</v>
+        <v>5.128205128205</v>
       </c>
       <c r="I21" s="17">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="J21" s="17">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="K21" s="18">
-        <v>20.512820512820</v>
+        <v>14.942528735632</v>
       </c>
       <c r="L21" s="18">
-        <v>1.438848920863</v>
+        <v>0.671140939597</v>
       </c>
       <c r="M21" s="18">
-        <v>14.17004048583</v>
+        <v>12.359550561797</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.626620570440</v>
+        <v>-75.708502024291</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,14 +1191,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
@@ -1210,10 +1210,10 @@
         <v>-80</v>
       </c>
       <c r="L22" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="M22" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,11 +1226,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1245,16 +1245,16 @@
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K23" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="M23" s="15">
         <v>-42.857142857142</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-63.636363636363</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.043478260869</v>
+        <v>-12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>-0.946372239747</v>
       </c>
       <c r="L24" s="15">
-        <v>8.118081180811</v>
+        <v>9.790209790209</v>
       </c>
       <c r="M24" s="15">
-        <v>32.579185520362</v>
+        <v>35.930735930735</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
+        <v>-23.529411764705</v>
+      </c>
+      <c r="F25" s="14">
+        <v>59</v>
+      </c>
+      <c r="G25" s="14">
+        <v>67</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-11.940298507462</v>
+      </c>
+      <c r="I25" s="14">
+        <v>230</v>
+      </c>
+      <c r="J25" s="14">
+        <v>262</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-12.213740458015</v>
+      </c>
+      <c r="L25" s="15">
         <v>0</v>
-      </c>
-      <c r="F25" s="14">
-        <v>60</v>
-      </c>
-      <c r="G25" s="14">
-        <v>79</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-24.050632911392</v>
-      </c>
-      <c r="I25" s="14">
-        <v>217</v>
-      </c>
-      <c r="J25" s="14">
-        <v>245</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-11.428571428571</v>
-      </c>
-      <c r="L25" s="15">
-        <v>0.462962962962</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H26" s="15">
-        <v>90.909090909090</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K26" s="15">
-        <v>31.914893617021</v>
+        <v>16.363636363636</v>
       </c>
       <c r="L26" s="15">
-        <v>21.568627450980</v>
+        <v>18.518518518518</v>
       </c>
       <c r="M26" s="15">
-        <v>14.814814814814</v>
+        <v>8.474576271186</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1399,11 +1399,11 @@
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-50</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,43 +1543,43 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="15">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -567,7 +567,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -884,11 +884,11 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -913,22 +913,22 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="15">
         <v>2</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="15">
         <v>3</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="14">
         <v>0</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="14">
         <v>0</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="14">
         <v>-71.428571428571</v>
       </c>
     </row>
@@ -936,205 +936,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>5</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-80</v>
-      </c>
-      <c r="I16" s="14">
-        <v>18</v>
-      </c>
-      <c r="J16" s="14">
-        <v>20</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-10</v>
-      </c>
-      <c r="L16" s="15">
-        <v>-28</v>
-      </c>
-      <c r="M16" s="15">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="N16" s="15">
-        <v>-88.461538461538</v>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="15">
+        <v>2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-50</v>
+      </c>
+      <c r="I16" s="15">
+        <v>19</v>
+      </c>
+      <c r="J16" s="15">
+        <v>22</v>
+      </c>
+      <c r="K16" s="14">
+        <v>-13.636363636363</v>
+      </c>
+      <c r="L16" s="14">
+        <v>-24</v>
+      </c>
+      <c r="M16" s="14">
+        <v>-13.636363636363</v>
+      </c>
+      <c r="N16" s="14">
+        <v>-88.690476190476</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>1</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="14">
-        <v>7</v>
-      </c>
-      <c r="G17" s="14">
+      <c r="D17" s="15">
         <v>4</v>
       </c>
-      <c r="H17" s="15">
-        <v>75</v>
-      </c>
-      <c r="I17" s="14">
-        <v>32</v>
-      </c>
-      <c r="J17" s="14">
-        <v>16</v>
-      </c>
-      <c r="K17" s="15">
-        <v>100</v>
-      </c>
-      <c r="L17" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="M17" s="15">
-        <v>68.421052631578</v>
-      </c>
-      <c r="N17" s="15">
-        <v>23.076923076923</v>
+      <c r="E17" s="14">
+        <v>-75</v>
+      </c>
+      <c r="F17" s="15">
+        <v>6</v>
+      </c>
+      <c r="G17" s="15">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>0</v>
+      </c>
+      <c r="I17" s="15">
+        <v>34</v>
+      </c>
+      <c r="J17" s="15">
+        <v>20</v>
+      </c>
+      <c r="K17" s="14">
+        <v>70</v>
+      </c>
+      <c r="L17" s="14">
+        <v>17.241379310344</v>
+      </c>
+      <c r="M17" s="14">
+        <v>61.904761904761</v>
+      </c>
+      <c r="N17" s="14">
+        <v>25.925925925925</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>6</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F18" s="14">
-        <v>11</v>
-      </c>
-      <c r="G18" s="14">
-        <v>11</v>
-      </c>
-      <c r="H18" s="15">
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
         <v>0</v>
       </c>
-      <c r="I18" s="14">
-        <v>44</v>
-      </c>
-      <c r="J18" s="14">
-        <v>47</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-6.382978723404</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-13.725490196078</v>
-      </c>
-      <c r="M18" s="15">
-        <v>29.411764705882</v>
-      </c>
-      <c r="N18" s="15">
-        <v>-79.245283018867</v>
+      <c r="F18" s="15">
+        <v>10</v>
+      </c>
+      <c r="G18" s="15">
+        <v>10</v>
+      </c>
+      <c r="H18" s="14">
+        <v>0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>45</v>
+      </c>
+      <c r="J18" s="15">
+        <v>48</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-6.25</v>
+      </c>
+      <c r="L18" s="14">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="M18" s="14">
+        <v>28.571428571428</v>
+      </c>
+      <c r="N18" s="14">
+        <v>-79.452054794520</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="14">
-        <v>12</v>
-      </c>
-      <c r="D19" s="14">
-        <v>19</v>
-      </c>
-      <c r="E19" s="15">
-        <v>-36.842105263157</v>
-      </c>
-      <c r="F19" s="14">
-        <v>57</v>
-      </c>
-      <c r="G19" s="14">
-        <v>56</v>
-      </c>
-      <c r="H19" s="15">
-        <v>1.785714285714</v>
-      </c>
-      <c r="I19" s="14">
-        <v>192</v>
-      </c>
-      <c r="J19" s="14">
-        <v>168</v>
-      </c>
-      <c r="K19" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="L19" s="15">
-        <v>3.783783783783</v>
-      </c>
-      <c r="M19" s="15">
-        <v>3.225806451612</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-63.567362428842</v>
+      <c r="C19" s="15">
+        <v>10</v>
+      </c>
+      <c r="D19" s="15">
+        <v>14</v>
+      </c>
+      <c r="E19" s="14">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="F19" s="15">
+        <v>50</v>
+      </c>
+      <c r="G19" s="15">
+        <v>61</v>
+      </c>
+      <c r="H19" s="14">
+        <v>-18.032786885245</v>
+      </c>
+      <c r="I19" s="15">
+        <v>202</v>
+      </c>
+      <c r="J19" s="15">
+        <v>182</v>
+      </c>
+      <c r="K19" s="14">
+        <v>10.989010989011</v>
+      </c>
+      <c r="L19" s="14">
+        <v>2.538071065989</v>
+      </c>
+      <c r="M19" s="14">
+        <v>3.061224489795</v>
+      </c>
+      <c r="N19" s="14">
+        <v>-63.734290843806</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
-        <v>5</v>
-      </c>
-      <c r="G20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
+        <v>3</v>
+      </c>
+      <c r="G20" s="15">
         <v>2</v>
       </c>
-      <c r="H20" s="15">
-        <v>150</v>
-      </c>
-      <c r="I20" s="14">
+      <c r="H20" s="14">
+        <v>50</v>
+      </c>
+      <c r="I20" s="15">
         <v>12</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="15">
         <v>7</v>
       </c>
-      <c r="K20" s="15">
+      <c r="K20" s="14">
         <v>71.428571428571</v>
       </c>
-      <c r="L20" s="15">
-        <v>71.428571428571</v>
-      </c>
-      <c r="M20" s="15">
+      <c r="L20" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M20" s="14">
         <v>140</v>
       </c>
-      <c r="N20" s="15">
-        <v>-96.091205211726</v>
+      <c r="N20" s="14">
+        <v>-96.341463414634</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.740740740740</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>5.128205128205</v>
+        <v>-14.457831325301</v>
       </c>
       <c r="I21" s="17">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="J21" s="17">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="K21" s="18">
-        <v>14.942528735632</v>
+        <v>11.347517730496</v>
       </c>
       <c r="L21" s="18">
-        <v>0.671140939597</v>
+        <v>0.319488817891</v>
       </c>
       <c r="M21" s="18">
-        <v>12.359550561797</v>
+        <v>11.347517730496</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.708502024291</v>
+        <v>-75.975516449885</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1200,20 +1200,20 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="15">
         <v>1</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="15">
         <v>5</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="14">
         <v>-80</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="14">
         <v>-90.909090909090</v>
       </c>
-      <c r="M22" s="15">
-        <v>-87.5</v>
+      <c r="M22" s="14">
+        <v>-88.888888888888</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1226,35 +1226,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <v>2</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="14">
         <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
+      <c r="G23" s="15">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
         <v>-100</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="15">
         <v>4</v>
       </c>
-      <c r="J23" s="14">
-        <v>9</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M23" s="15">
-        <v>-42.857142857142</v>
+      <c r="J23" s="15">
+        <v>11</v>
+      </c>
+      <c r="K23" s="14">
+        <v>-63.636363636363</v>
+      </c>
+      <c r="L23" s="14">
+        <v>-69.230769230769</v>
+      </c>
+      <c r="M23" s="14">
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1264,38 +1264,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="14">
-        <v>21</v>
-      </c>
-      <c r="D24" s="14">
-        <v>24</v>
-      </c>
-      <c r="E24" s="15">
-        <v>-12.5</v>
-      </c>
-      <c r="F24" s="14">
-        <v>90</v>
-      </c>
-      <c r="G24" s="14">
-        <v>90</v>
-      </c>
-      <c r="H24" s="15">
-        <v>0</v>
-      </c>
-      <c r="I24" s="14">
-        <v>314</v>
-      </c>
-      <c r="J24" s="14">
-        <v>317</v>
-      </c>
-      <c r="K24" s="15">
-        <v>-0.946372239747</v>
-      </c>
-      <c r="L24" s="15">
-        <v>9.790209790209</v>
-      </c>
-      <c r="M24" s="15">
-        <v>35.930735930735</v>
+      <c r="C24" s="15">
+        <v>28</v>
+      </c>
+      <c r="D24" s="15">
+        <v>20</v>
+      </c>
+      <c r="E24" s="14">
+        <v>40</v>
+      </c>
+      <c r="F24" s="15">
+        <v>97</v>
+      </c>
+      <c r="G24" s="15">
+        <v>85</v>
+      </c>
+      <c r="H24" s="14">
+        <v>14.117647058823</v>
+      </c>
+      <c r="I24" s="15">
+        <v>342</v>
+      </c>
+      <c r="J24" s="15">
+        <v>337</v>
+      </c>
+      <c r="K24" s="14">
+        <v>1.483679525222</v>
+      </c>
+      <c r="L24" s="14">
+        <v>13.245033112582</v>
+      </c>
+      <c r="M24" s="14">
+        <v>35.714285714285</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>13</v>
-      </c>
-      <c r="D25" s="14">
+      <c r="C25" s="15">
         <v>17</v>
       </c>
-      <c r="E25" s="15">
-        <v>-23.529411764705</v>
-      </c>
-      <c r="F25" s="14">
-        <v>59</v>
-      </c>
-      <c r="G25" s="14">
-        <v>67</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-11.940298507462</v>
-      </c>
-      <c r="I25" s="14">
-        <v>230</v>
-      </c>
-      <c r="J25" s="14">
-        <v>262</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-12.213740458015</v>
-      </c>
-      <c r="L25" s="15">
-        <v>0</v>
+      <c r="D25" s="15">
+        <v>16</v>
+      </c>
+      <c r="E25" s="14">
+        <v>6.25</v>
+      </c>
+      <c r="F25" s="15">
+        <v>61</v>
+      </c>
+      <c r="G25" s="15">
+        <v>64</v>
+      </c>
+      <c r="H25" s="14">
+        <v>-4.6875</v>
+      </c>
+      <c r="I25" s="15">
+        <v>247</v>
+      </c>
+      <c r="J25" s="15">
+        <v>278</v>
+      </c>
+      <c r="K25" s="14">
+        <v>-11.151079136690</v>
+      </c>
+      <c r="L25" s="14">
+        <v>1.646090534979</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="14">
-        <v>2</v>
-      </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F26" s="14">
-        <v>10</v>
-      </c>
-      <c r="G26" s="14">
-        <v>15</v>
-      </c>
-      <c r="H26" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I26" s="14">
-        <v>64</v>
-      </c>
-      <c r="J26" s="14">
-        <v>55</v>
-      </c>
-      <c r="K26" s="15">
-        <v>16.363636363636</v>
-      </c>
-      <c r="L26" s="15">
-        <v>18.518518518518</v>
-      </c>
-      <c r="M26" s="15">
-        <v>8.474576271186</v>
+      <c r="C26" s="15">
+        <v>3</v>
+      </c>
+      <c r="D26" s="15">
+        <v>7</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="F26" s="15">
+        <v>7</v>
+      </c>
+      <c r="G26" s="15">
+        <v>19</v>
+      </c>
+      <c r="H26" s="14">
+        <v>-63.157894736842</v>
+      </c>
+      <c r="I26" s="15">
+        <v>66</v>
+      </c>
+      <c r="J26" s="15">
+        <v>62</v>
+      </c>
+      <c r="K26" s="14">
+        <v>6.451612903225</v>
+      </c>
+      <c r="L26" s="14">
+        <v>17.857142857142</v>
+      </c>
+      <c r="M26" s="14">
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,8 +1396,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1405,16 +1405,16 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="15">
         <v>2</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="15">
         <v>5</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="14">
         <v>-60</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1437,25 +1437,25 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="14">
-        <v>5</v>
-      </c>
-      <c r="G28" s="14">
+      <c r="F28" s="15">
         <v>4</v>
       </c>
-      <c r="H28" s="15">
-        <v>25</v>
-      </c>
-      <c r="I28" s="14">
+      <c r="G28" s="15">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>300</v>
+      </c>
+      <c r="I28" s="15">
         <v>11</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="15">
         <v>9</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="14">
         <v>22.222222222222</v>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="14">
         <v>175</v>
       </c>
       <c r="M28" s="13" t="s">
@@ -1487,7 +1487,7 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="15">
         <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
@@ -1502,7 +1502,7 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="15">
         <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
@@ -1543,7 +1543,7 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="14">
         <v>0</v>
       </c>
     </row>
@@ -1551,34 +1551,34 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="G31" s="15">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
-      </c>
-      <c r="I31" s="14">
+      <c r="H31" s="14">
+        <v>-50</v>
+      </c>
+      <c r="I31" s="15">
         <v>7</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="15">
         <v>3</v>
       </c>
-      <c r="K31" s="15">
+      <c r="K31" s="14">
         <v>133.333333333333</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="14">
         <v>600</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1637,7 +1637,7 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="14">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -1745,16 +1745,16 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>3</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="15">
         <v>1</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <v>3</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="15">
         <v>1</v>
       </c>
       <c r="K39" s="13" t="s">
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>13</v>
       </c>
-      <c r="E40" s="14">
-        <v>20</v>
-      </c>
-      <c r="G40" s="14">
+      <c r="E40" s="15">
+        <v>20</v>
+      </c>
+      <c r="G40" s="15">
         <v>17</v>
       </c>
-      <c r="I40" s="14">
+      <c r="I40" s="15">
         <v>7</v>
       </c>
-      <c r="J40" s="14">
+      <c r="J40" s="15">
         <v>8</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="14">
         <v>14.285714285714</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="14">
         <v>-52.941176470588</v>
       </c>
-      <c r="M40" s="15">
+      <c r="M40" s="14">
         <v>-60</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="14">
         <v>-38.461538461538</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>978</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="15">
         <v>610</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <v>283</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="15">
         <v>174</v>
       </c>
-      <c r="J41" s="14">
+      <c r="J41" s="15">
         <v>102</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>-41.379310344827</v>
       </c>
-      <c r="L41" s="15">
+      <c r="L41" s="14">
         <v>-63.957597173144</v>
       </c>
-      <c r="M41" s="15">
+      <c r="M41" s="14">
         <v>-83.278688524590</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="14">
         <v>-89.570552147239</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>129</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="15">
         <v>99</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <v>95</v>
       </c>
-      <c r="I42" s="14">
+      <c r="I42" s="15">
         <v>112</v>
       </c>
-      <c r="J42" s="14">
+      <c r="J42" s="15">
         <v>99</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>-11.607142857142</v>
       </c>
-      <c r="L42" s="15">
+      <c r="L42" s="14">
         <v>4.210526315789</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="14">
         <v>0</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="14">
         <v>-23.255813953488</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>1305</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="15">
         <v>921</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <v>324</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="15">
         <v>162</v>
       </c>
-      <c r="J43" s="14">
+      <c r="J43" s="15">
         <v>135</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>-16.666666666666</v>
       </c>
-      <c r="L43" s="15">
+      <c r="L43" s="14">
         <v>-58.333333333333</v>
       </c>
-      <c r="M43" s="15">
+      <c r="M43" s="14">
         <v>-85.342019543973</v>
       </c>
-      <c r="N43" s="15">
+      <c r="N43" s="14">
         <v>-89.655172413793</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>2235</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="15">
         <v>1798</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <v>813</v>
       </c>
-      <c r="I44" s="14">
+      <c r="I44" s="15">
         <v>877</v>
       </c>
-      <c r="J44" s="14">
+      <c r="J44" s="15">
         <v>730</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>-16.761687571265</v>
       </c>
-      <c r="L44" s="15">
+      <c r="L44" s="14">
         <v>-10.209102091020</v>
       </c>
-      <c r="M44" s="15">
+      <c r="M44" s="14">
         <v>-59.399332591768</v>
       </c>
-      <c r="N44" s="15">
+      <c r="N44" s="14">
         <v>-67.337807606264</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>1679</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="15">
         <v>1153</v>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <v>393</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="15">
         <v>160</v>
       </c>
-      <c r="J45" s="14">
+      <c r="J45" s="15">
         <v>42</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="14">
         <v>-73.75</v>
       </c>
-      <c r="L45" s="15">
+      <c r="L45" s="14">
         <v>-89.312977099236</v>
       </c>
-      <c r="M45" s="15">
+      <c r="M45" s="14">
         <v>-96.357328707719</v>
       </c>
-      <c r="N45" s="15">
+      <c r="N45" s="14">
         <v>-97.498511018463</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-13.636363636363</v>
+        <v>-16</v>
       </c>
       <c r="L16" s="14">
-        <v>-24</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M16" s="14">
-        <v>-13.636363636363</v>
+        <v>-16</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.690476190476</v>
+        <v>-87.861271676300</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
         <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>70</v>
+        <v>68.181818181818</v>
       </c>
       <c r="L17" s="14">
-        <v>17.241379310344</v>
+        <v>23.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>61.904761904761</v>
+        <v>68.181818181818</v>
       </c>
       <c r="N17" s="14">
-        <v>25.925925925925</v>
+        <v>37.037037037037</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
         <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J18" s="15">
         <v>48</v>
       </c>
       <c r="K18" s="14">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-11.764705882352</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M18" s="14">
-        <v>28.571428571428</v>
+        <v>29.729729729729</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.452054794520</v>
+        <v>-79.574468085106</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>-6.25</v>
       </c>
       <c r="F19" s="15">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="15">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.032786885245</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="I19" s="15">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="J19" s="15">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="K19" s="14">
-        <v>10.989010989011</v>
+        <v>9.595959595959</v>
       </c>
       <c r="L19" s="14">
-        <v>2.538071065989</v>
+        <v>0.930232558139</v>
       </c>
       <c r="M19" s="14">
-        <v>3.061224489795</v>
+        <v>6.896551724137</v>
       </c>
       <c r="N19" s="14">
-        <v>-63.734290843806</v>
+        <v>-63.651591289782</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>71.428571428571</v>
+        <v>20</v>
       </c>
       <c r="L20" s="14">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M20" s="14">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.341463414634</v>
+        <v>-96.638655462184</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.095238095238</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.457831325301</v>
+        <v>-15.294117647058</v>
       </c>
       <c r="I21" s="17">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="J21" s="17">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="K21" s="18">
-        <v>11.347517730496</v>
+        <v>10.130718954248</v>
       </c>
       <c r="L21" s="18">
-        <v>0.319488817891</v>
+        <v>0.597014925373</v>
       </c>
       <c r="M21" s="18">
-        <v>11.347517730496</v>
+        <v>13.851351351351</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.975516449885</v>
+        <v>-75.894134477825</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,29 +1185,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L22" s="14">
         <v>-90.909090909090</v>
@@ -1223,38 +1223,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" s="14">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M23" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>40</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G24" s="15">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H24" s="14">
-        <v>14.117647058823</v>
+        <v>3.296703296703</v>
       </c>
       <c r="I24" s="15">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="J24" s="15">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="K24" s="14">
-        <v>1.483679525222</v>
+        <v>1.662049861495</v>
       </c>
       <c r="L24" s="14">
-        <v>13.245033112582</v>
+        <v>11.890243902439</v>
       </c>
       <c r="M24" s="14">
-        <v>35.714285714285</v>
+        <v>34.926470588235</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,13 +1306,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
         <v>16</v>
       </c>
       <c r="E25" s="14">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="F25" s="15">
         <v>61</v>
@@ -1324,16 +1324,16 @@
         <v>-4.6875</v>
       </c>
       <c r="I25" s="15">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="J25" s="15">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.151079136690</v>
+        <v>-10.544217687074</v>
       </c>
       <c r="L25" s="14">
-        <v>1.646090534979</v>
+        <v>1.153846153846</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>6</v>
+      </c>
+      <c r="D26" s="15">
         <v>3</v>
       </c>
-      <c r="D26" s="15">
-        <v>7</v>
-      </c>
       <c r="E26" s="14">
-        <v>-57.142857142857</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G26" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-63.157894736842</v>
+        <v>-45</v>
       </c>
       <c r="I26" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J26" s="15">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K26" s="14">
-        <v>6.451612903225</v>
+        <v>10.769230769230</v>
       </c>
       <c r="L26" s="14">
-        <v>17.857142857142</v>
+        <v>20</v>
       </c>
       <c r="M26" s="14">
-        <v>0</v>
+        <v>7.462686567164</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,29 +1431,29 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="L28" s="14">
         <v>175</v>
@@ -1564,10 +1564,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>7</v>
@@ -1579,7 +1579,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -898,35 +898,35 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
         <v>-75</v>
@@ -936,23 +936,23 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F16" s="15">
-        <v>4</v>
-      </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
         <v>21</v>
@@ -964,13 +964,13 @@
         <v>-16</v>
       </c>
       <c r="L16" s="14">
+        <v>-30</v>
+      </c>
+      <c r="M16" s="14">
         <v>-19.230769230769</v>
       </c>
-      <c r="M16" s="14">
-        <v>-16</v>
-      </c>
       <c r="N16" s="14">
-        <v>-87.861271676300</v>
+        <v>-88.709677419354</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15">
-        <v>2</v>
-      </c>
-      <c r="E17" s="14">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="15">
         <v>6</v>
       </c>
       <c r="H17" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J17" s="15">
         <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>68.181818181818</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L17" s="14">
-        <v>23.333333333333</v>
+        <v>18.75</v>
       </c>
       <c r="M17" s="14">
-        <v>68.181818181818</v>
+        <v>58.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>37.037037037037</v>
+        <v>31.034482758620</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
         <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J18" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-7.692307692307</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M18" s="14">
-        <v>29.729729729729</v>
+        <v>35.135135135135</v>
       </c>
       <c r="N18" s="14">
-        <v>-79.574468085106</v>
+        <v>-80.158730158730</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>16</v>
+      </c>
+      <c r="D19" s="15">
         <v>15</v>
       </c>
-      <c r="D19" s="15">
-        <v>16</v>
-      </c>
       <c r="E19" s="14">
-        <v>-6.25</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G19" s="15">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H19" s="14">
-        <v>-16.949152542372</v>
+        <v>-15.625</v>
       </c>
       <c r="I19" s="15">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="J19" s="15">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="K19" s="14">
-        <v>9.595959595959</v>
+        <v>10.328638497652</v>
       </c>
       <c r="L19" s="14">
-        <v>0.930232558139</v>
+        <v>1.731601731601</v>
       </c>
       <c r="M19" s="14">
-        <v>6.896551724137</v>
+        <v>8.294930875576</v>
       </c>
       <c r="N19" s="14">
-        <v>-63.651591289782</v>
+        <v>-63.050314465408</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,20 +1103,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
@@ -1128,13 +1128,13 @@
         <v>20</v>
       </c>
       <c r="L20" s="14">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.638655462184</v>
+        <v>-96.866840731070</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-4.166666666666</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F21" s="17">
         <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.294117647058</v>
+        <v>-20</v>
       </c>
       <c r="I21" s="17">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="J21" s="17">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="K21" s="18">
-        <v>10.130718954248</v>
+        <v>10.493827160493</v>
       </c>
       <c r="L21" s="18">
-        <v>0.597014925373</v>
+        <v>-0.831024930747</v>
       </c>
       <c r="M21" s="18">
-        <v>13.851351351351</v>
+        <v>13.291139240506</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.894134477825</v>
+        <v>-76.053511705685</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1204,16 +1204,16 @@
         <v>1</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L22" s="14">
-        <v>-90.909090909090</v>
+        <v>-92.307692307692</v>
       </c>
       <c r="M22" s="14">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,14 +1223,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>1</v>
@@ -1251,7 +1251,7 @@
         <v>-58.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M23" s="14">
         <v>-44.444444444444</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>8.333333333333</v>
+        <v>-21.875</v>
       </c>
       <c r="F24" s="15">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G24" s="15">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H24" s="14">
-        <v>3.296703296703</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="15">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="J24" s="15">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="K24" s="14">
-        <v>1.662049861495</v>
+        <v>-0.508905852417</v>
       </c>
       <c r="L24" s="14">
-        <v>11.890243902439</v>
+        <v>6.830601092896</v>
       </c>
       <c r="M24" s="14">
-        <v>34.926470588235</v>
+        <v>32.993197278911</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" s="15">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
-        <v>-6.25</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" s="15">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H25" s="14">
-        <v>-4.6875</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="I25" s="15">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="J25" s="15">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="K25" s="14">
-        <v>-10.544217687074</v>
+        <v>-12.893081761006</v>
       </c>
       <c r="L25" s="14">
-        <v>1.153846153846</v>
+        <v>-3.819444444444</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
         <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26" s="15">
         <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="I26" s="15">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J26" s="15">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K26" s="14">
-        <v>10.769230769230</v>
+        <v>13.432835820895</v>
       </c>
       <c r="L26" s="14">
-        <v>20</v>
+        <v>22.580645161290</v>
       </c>
       <c r="M26" s="14">
-        <v>7.462686567164</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,29 +1390,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>-33.333333333333</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
+        <v>12</v>
+      </c>
+      <c r="J28" s="15">
         <v>11</v>
       </c>
-      <c r="J28" s="15">
-        <v>10</v>
-      </c>
       <c r="K28" s="14">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>7</v>
@@ -1613,29 +1613,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>-100</v>
       </c>
       <c r="L33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-16</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L16" s="14">
-        <v>-30</v>
+        <v>-28.125</v>
       </c>
       <c r="M16" s="14">
-        <v>-19.230769230769</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.709677419354</v>
+        <v>-88.324873096446</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="15">
+        <v>3</v>
+      </c>
+      <c r="E17" s="14">
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>72.727272727272</v>
+        <v>68</v>
       </c>
       <c r="L17" s="14">
-        <v>18.75</v>
+        <v>20</v>
       </c>
       <c r="M17" s="14">
-        <v>58.333333333333</v>
+        <v>68</v>
       </c>
       <c r="N17" s="14">
-        <v>31.034482758620</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
         <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-11.111111111111</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L18" s="14">
-        <v>-9.090909090909</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M18" s="14">
-        <v>35.135135135135</v>
+        <v>26.829268292682</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.158730158730</v>
+        <v>-80.524344569288</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>6.666666666666</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F19" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G19" s="15">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H19" s="14">
-        <v>-15.625</v>
+        <v>-1.694915254237</v>
       </c>
       <c r="I19" s="15">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="J19" s="15">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="K19" s="14">
-        <v>10.328638497652</v>
+        <v>11.013215859030</v>
       </c>
       <c r="L19" s="14">
-        <v>1.731601731601</v>
+        <v>3.278688524590</v>
       </c>
       <c r="M19" s="14">
-        <v>8.294930875576</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N19" s="14">
-        <v>-63.050314465408</v>
+        <v>-62.331838565022</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>1</v>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="15">
         <v>12</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L20" s="14">
-        <v>9.090909090909</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M20" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.866840731070</v>
+        <v>-97.073170731707</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>5.555555555555</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-20</v>
+        <v>-10.112359550561</v>
       </c>
       <c r="I21" s="17">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="J21" s="17">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="K21" s="18">
-        <v>10.493827160493</v>
+        <v>9.428571428571</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.831024930747</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>13.291139240506</v>
+        <v>13.988095238095</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.053511705685</v>
+        <v>-75.790139064475</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1223,8 +1223,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,28 +1233,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="15">
         <v>12</v>
       </c>
       <c r="K23" s="14">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="14">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="14">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E24" s="14">
-        <v>-21.875</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F24" s="15">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G24" s="15">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H24" s="14">
-        <v>-1</v>
+        <v>-14.035087719298</v>
       </c>
       <c r="I24" s="15">
-        <v>391</v>
+        <v>410</v>
       </c>
       <c r="J24" s="15">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="K24" s="14">
-        <v>-0.508905852417</v>
+        <v>-4.872389791183</v>
       </c>
       <c r="L24" s="14">
-        <v>6.830601092896</v>
+        <v>3.015075376884</v>
       </c>
       <c r="M24" s="14">
-        <v>32.993197278911</v>
+        <v>29.746835443038</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,13 +1306,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E25" s="14">
-        <v>-41.666666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F25" s="15">
         <v>60</v>
@@ -1324,16 +1324,16 @@
         <v>-17.808219178082</v>
       </c>
       <c r="I25" s="15">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="J25" s="15">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="K25" s="14">
-        <v>-12.893081761006</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="L25" s="14">
-        <v>-3.819444444444</v>
+        <v>-7.348242811501</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G26" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J26" s="15">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K26" s="14">
-        <v>13.432835820895</v>
+        <v>10.958904109589</v>
       </c>
       <c r="L26" s="14">
-        <v>22.580645161290</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M26" s="14">
-        <v>0</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1400,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1409,10 +1409,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L27" s="14">
         <v>-33.333333333333</v>
@@ -1438,25 +1438,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
+        <v>13</v>
+      </c>
+      <c r="J28" s="15">
         <v>12</v>
       </c>
-      <c r="J28" s="15">
-        <v>11</v>
-      </c>
       <c r="K28" s="14">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>200</v>
+        <v>116.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1610,35 +1610,35 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="15">
+      <c r="C33" s="15">
         <v>1</v>
       </c>
-      <c r="E33" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="15">
         <v>1</v>
       </c>
       <c r="H33" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I33" s="15">
+        <v>1</v>
       </c>
       <c r="J33" s="15">
         <v>1</v>
       </c>
       <c r="K33" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-020pct.xlsx
+++ b/data/source/weekly/cs-en-us-020pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -929,7 +929,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -939,38 +939,38 @@
       <c r="C16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
+        <v>6</v>
+      </c>
+      <c r="G16" s="15">
         <v>5</v>
       </c>
-      <c r="G16" s="15">
-        <v>7</v>
-      </c>
       <c r="H16" s="14">
-        <v>-28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="15">
         <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-14.814814814814</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.125</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M16" s="14">
-        <v>-20.689655172413</v>
+        <v>-21.875</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.324873096446</v>
+        <v>-88.425925925925</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J17" s="15">
         <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="L17" s="14">
-        <v>20</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M17" s="14">
-        <v>68</v>
+        <v>69.230769230769</v>
       </c>
       <c r="N17" s="14">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
         <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I18" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J18" s="15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K18" s="14">
-        <v>-3.703703703703</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="L18" s="14">
-        <v>-8.771929824561</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>26.829268292682</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N18" s="14">
-        <v>-80.524344569288</v>
+        <v>-80.575539568345</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
-        <v>21.428571428571</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F19" s="15">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="15">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H19" s="14">
-        <v>-1.694915254237</v>
+        <v>-10.9375</v>
       </c>
       <c r="I19" s="15">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="J19" s="15">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="K19" s="14">
-        <v>11.013215859030</v>
+        <v>6.097560975609</v>
       </c>
       <c r="L19" s="14">
-        <v>3.278688524590</v>
+        <v>3.162055335968</v>
       </c>
       <c r="M19" s="14">
-        <v>10.526315789473</v>
+        <v>7.407407407407</v>
       </c>
       <c r="N19" s="14">
-        <v>-62.331838565022</v>
+        <v>-62.714285714285</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,11 +1103,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>3</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1128,13 +1128,13 @@
         <v>-7.692307692307</v>
       </c>
       <c r="L20" s="14">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="14">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.073170731707</v>
+        <v>-97.183098591549</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.846153846153</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.112359550561</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="J21" s="17">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="K21" s="18">
-        <v>9.428571428571</v>
+        <v>7.567567567567</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>-1.728395061728</v>
       </c>
       <c r="M21" s="18">
-        <v>13.988095238095</v>
+        <v>11.484593837535</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.790139064475</v>
+        <v>-76.067348165965</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,8 +1223,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1236,10 +1236,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
         <v>6</v>
@@ -1251,7 +1251,7 @@
         <v>-50</v>
       </c>
       <c r="L23" s="14">
-        <v>-60</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="M23" s="14">
         <v>-33.333333333333</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" s="14">
-        <v>-47.368421052631</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="F24" s="15">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="15">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H24" s="14">
-        <v>-14.035087719298</v>
+        <v>-24.427480916030</v>
       </c>
       <c r="I24" s="15">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="J24" s="15">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="K24" s="14">
-        <v>-4.872389791183</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="L24" s="14">
-        <v>3.015075376884</v>
+        <v>2.097902097902</v>
       </c>
       <c r="M24" s="14">
-        <v>29.746835443038</v>
+        <v>29.203539823008</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D25" s="15">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E25" s="14">
-        <v>-23.529411764705</v>
+        <v>-8</v>
       </c>
       <c r="F25" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G25" s="15">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H25" s="14">
-        <v>-17.808219178082</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="I25" s="15">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="J25" s="15">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="K25" s="14">
-        <v>-13.432835820895</v>
+        <v>-13.055555555555</v>
       </c>
       <c r="L25" s="14">
-        <v>-7.348242811501</v>
+        <v>-6.006006006006</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I26" s="15">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J26" s="15">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K26" s="14">
-        <v>10.958904109589</v>
+        <v>14.473684210526</v>
       </c>
       <c r="L26" s="14">
-        <v>17.391304347826</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M26" s="14">
-        <v>-7.954545454545</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1428,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
         <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>8.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L28" s="14">
         <v>116.666666666667</v>
@@ -1496,8 +1496,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1537,8 +1537,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1579,7 +1579,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
